--- a/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Masas y Fermentación" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cremas y Rellenos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Decoración y Acabado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Masas y Fermentación" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cremas y Rellenos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decoración y Acabado" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Masas y Fermentación'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cremas y Rellenos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Decoración y Acabado'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +96,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -125,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -147,54 +157,104 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -556,13 +616,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -570,6 +631,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -598,8 +660,24 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -608,18 +686,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,10 +714,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -679,18 +758,16 @@
           <t xml:space="preserve">  Masas de Bollería (Croissant, Brioche, Danesa)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -716,10 +793,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -745,10 +820,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -774,14 +847,12 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Amasar en planetaria (1ª velocidad 4 min, 2ª velocidad 8-10 min)</t>
+          <t>Amasar corto en planetaria (1ª velocidad 3-4 min, 2ª velocidad 2-3 min): el gluten se termina de desarrollar en el laminado</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -803,14 +874,12 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Control de temperatura de masa al salir (24-26 °C ideal)</t>
+          <t>Control de temperatura de masa al salir (22-24 °C; 20-22 °C si va directa a bloque de frío)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -832,10 +901,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -861,10 +928,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -890,10 +955,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -919,10 +982,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -948,10 +1009,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -977,10 +1036,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1005,24 +1062,23 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Masas de Pan Artesano</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1048,10 +1104,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1077,10 +1131,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1106,10 +1158,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="25" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1135,10 +1185,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1164,10 +1212,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="25" t="n">
+        <v>17</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1193,10 +1239,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="25" t="n">
+        <v>18</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1221,24 +1265,23 @@
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="15" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Masas Quebradas y Bases</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="25" t="n">
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1264,10 +1307,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="25" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1293,10 +1334,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="25" t="n">
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1322,10 +1361,8 @@
       <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="25" t="n">
+        <v>22</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1351,10 +1388,8 @@
       <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A32" s="25" t="n">
+        <v>23</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -1380,10 +1415,8 @@
       <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A33" s="25" t="n">
+        <v>24</v>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
@@ -1408,6 +1441,8 @@
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="15" t="n"/>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
@@ -1416,7 +1451,7 @@
       </c>
       <c r="D36" s="16">
         <f>COUNTIF(F5:F34,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
@@ -1427,6 +1462,7 @@
         <v>24</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
@@ -1434,13 +1470,17 @@
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
       <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F38" s="15" t="n"/>
-    </row>
+      <c r="G38" s="24" t="n"/>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
@@ -1460,11 +1500,20 @@
     <mergeCell ref="F38:G38"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F33" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1473,18 +1522,18 @@
   <sheetPr>
     <tabColor rgb="00E91E63"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1501,10 +1550,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1544,18 +1594,16 @@
           <t xml:space="preserve">  Cremas Base</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1581,10 +1629,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1610,10 +1656,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1639,10 +1683,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1668,10 +1710,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1697,10 +1737,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1726,10 +1764,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1754,24 +1790,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mousses y Rellenos</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1797,10 +1832,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1826,10 +1859,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1855,10 +1886,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1884,10 +1913,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1913,14 +1940,12 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Congelar entremets montados (mínimo 4h antes de glasear)</t>
+          <t>Congelar entremets montados para el glaseado de mañana (mín. 4 h en abatidor a −18 °C o 12 h en congelador)</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1941,24 +1966,23 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Coberturas y Acabados</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="25" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1984,10 +2008,8 @@
       <c r="G23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A24" s="25" t="n">
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -2013,10 +2035,8 @@
       <c r="G24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="25" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -2042,10 +2062,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="25" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2071,10 +2089,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="25" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2099,6 +2115,8 @@
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="15" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -2107,7 +2125,7 @@
       </c>
       <c r="D30" s="16">
         <f>COUNTIF(F5:F28,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
@@ -2118,6 +2136,7 @@
         <v>18</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
@@ -2125,13 +2144,17 @@
         </is>
       </c>
       <c r="B32" s="15" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
       <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F32" s="15" t="n"/>
-    </row>
+      <c r="G32" s="24" t="n"/>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
@@ -2151,11 +2174,20 @@
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2164,18 +2196,18 @@
   <sheetPr>
     <tabColor rgb="009C27B0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2192,10 +2224,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2235,22 +2268,20 @@
           <t xml:space="preserve">  Decoración de Tartas y Entremets</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Desmoldar entremets congelados</t>
+          <t>Desmoldar los entremets congelados el día anterior</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2272,10 +2303,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="25" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2301,10 +2330,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="25" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2330,10 +2357,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2359,14 +2384,12 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="25" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Montar tartas por encargo (según ficha de pedido)</t>
+          <t>Montar tartas por encargo (según la ficha de encargo de cada pedido)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -2388,10 +2411,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2416,24 +2437,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  Montaje de Vitrina</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="25" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2459,10 +2479,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="25" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2488,10 +2506,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="25" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2517,10 +2533,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="25" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2546,10 +2560,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="25" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2575,10 +2587,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="25" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2604,10 +2614,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="25" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -2632,6 +2640,8 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -2640,7 +2650,7 @@
       </c>
       <c r="D23" s="16">
         <f>COUNTIF(F5:F21,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
@@ -2651,6 +2661,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
@@ -2658,13 +2669,17 @@
         </is>
       </c>
       <c r="B25" s="15" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F25" s="15" t="n"/>
-    </row>
+      <c r="G25" s="24" t="n"/>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
@@ -2683,10 +2698,19 @@
     <mergeCell ref="B25:D25"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
@@ -254,6 +254,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -664,14 +674,15 @@
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -688,16 +699,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,25 +740,30 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>Parámetro / Objetivo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Hora Límite</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
       <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
@@ -763,7 +780,8 @@
       <c r="D5" s="23" t="n"/>
       <c r="E5" s="23" t="n"/>
       <c r="F5" s="23" t="n"/>
-      <c r="G5" s="24" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="25" t="n">
@@ -774,23 +792,28 @@
           <t>Verificar estado de masa madre / prefermento (olor, volumen, textura)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Dobla volumen en 3-4 h · olor láctico, nunca avinagrado</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
@@ -801,23 +824,28 @@
           <t>Refrescar masa madre si es necesario (alimentar con harina y agua)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Refresco 1:1:1 · reposo a 24-26 °C</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>05:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n">
@@ -828,23 +856,28 @@
           <t>Pesar ingredientes para masa de croissant (harina, mantequilla, levadura)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Harina W 300-330 · mantequilla de laminado 82 % MG</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>05:15</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="25" t="n">
@@ -855,23 +888,28 @@
           <t>Amasar corto en planetaria (1ª velocidad 3-4 min, 2ª velocidad 2-3 min): el gluten se termina de desarrollar en el laminado</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>1ª vel. 3-4 min · 2ª vel. 2-3 min</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>05:30</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="25" t="n">
@@ -882,23 +920,28 @@
           <t>Control de temperatura de masa al salir (22-24 °C; 20-22 °C si va directa a bloque de frío)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>22-24 °C · 20-22 °C si va a bloque de frío</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>05:45</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
@@ -906,26 +949,31 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Reposo en bloque en cámara (mínimo 1h a 4 °C)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+          <t>Bloque en frío antes de laminar (abatidor o cámara)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>1 h en abatidor o 12 h en cámara a 3-4 °C</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>05:45</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n">
@@ -933,26 +981,31 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Laminar con mantequilla (3 pliegues simples o 2 dobles)</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+          <t>Sacar del retardador la croissantería formada ayer y comprobar el punto de fermentación</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Fermentación controlada nocturna · sube a 24-26 °C · dobla volumen</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="25" t="n">
@@ -960,26 +1013,31 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Cortar y dar forma (croissant, pain au chocolat, trenza)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
+          <t>Pincelar y hornear la 1ª hornada del día para la apertura de la vitrina</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>190-200 °C · 14-18 min · en la vitrina antes de las 08:00</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="n">
@@ -987,26 +1045,31 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Fermentar en cámara controlada (28 °C, 75% humedad, 1.5-2h)</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+          <t>Laminar con mantequilla (3 pliegues simples o 2 dobles)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Masa y mantequilla a 12-14 °C · espesor final 3-3,5 mm</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
@@ -1014,26 +1077,31 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Pincelar con huevo antes de hornear</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Ayudante</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+          <t>Cortar y dar forma: una parte a la 2ª hornada de hoy y otra al retardador para mañana</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Croissant 65-70 g · pain au chocolat 70-75 g</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n">
@@ -1041,94 +1109,110 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Hornear (190-200 °C, 14-18 min según tamaño)</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-    </row>
-    <row r="17"/>
+          <t>Fermentar en cámara controlada sin superar los 28 °C (por encima funde la mantequilla del laminado)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>24-26 °C (28 °C techo) · 75-80 % HR · 2,5-3 h · dobla volumen</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Pincelar con huevo la 2ª hornada antes de hornear</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Huevo entero con una pizca de sal · capa fina</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Ayudante</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
+    </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Hornear la 2ª hornada de media mañana (190-200 °C, 14-18 min según tamaño)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>190-200 °C · 14-18 min</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Masas de Pan Artesano</t>
         </is>
       </c>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="24" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Verificar fermentación nocturna de masas (volumen, alveolos)</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Dividir y pesar porciones según formato (barra, hogaza, chapata)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>05:15</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="24" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="25" t="n">
@@ -1136,26 +1220,31 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Bolear y dar forma (tensión superficial correcta)</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
+          <t>Verificar fermentación nocturna de masas (volumen, alveolos)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>12-16 h a 4-6 °C</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="25" t="n">
@@ -1163,26 +1252,31 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Segunda fermentación en banastones / telas (45 min - 1h)</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>05:45</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
+          <t>Dividir y pesar porciones según formato (barra, hogaza, chapata)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Barra 250-280 g · hogaza 800-900 g</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="25" t="n">
@@ -1190,26 +1284,27 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Greñar / cortar con cuchilla antes de hornear</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+          <t>Bolear y dar forma (tensión superficial correcta)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="25" t="n">
@@ -1217,26 +1312,31 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Hornear con vapor (230-250 °C, vapor primeros 10 min)</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+          <t>Segunda fermentación en banastones / telas (45 min - 1h)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>45-60 min a 24-26 °C</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="25" t="n">
@@ -1244,94 +1344,110 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
+          <t>Greñar / cortar con cuchilla antes de hornear</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Cuchilla inclinada 30-45°</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Hornear con vapor: golpe de vapor al cargar y abrir el tiro al final</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>230-250 °C · vapor 3-5 min · tiro abierto los últimos 5-8 min</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
           <t>Enfriar en rejillas (no apilar, mínimo 30 min)</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Mín. 30 min · sin apilar</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>Ayudante</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="15" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Masas Quebradas y Bases</t>
         </is>
       </c>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="n">
-        <v>19</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Preparar masa sablée (mantequilla pomada + azúcar + harina)</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Preparar masa brisée para quiches/tartas saladas</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="n">
@@ -1339,26 +1455,31 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Estirar y forrar moldes de tarta</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Ayudante</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
+          <t>Preparar masa sablée (mantequilla pomada + azúcar + harina)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Mantequilla pomada a 18-20 °C</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="25" t="n">
@@ -1366,26 +1487,31 @@
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
-          <t>Hornear en blanco con pesos (180 °C, 15 min)</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
+          <t>Preparar masa brisée para quiches/tartas saladas</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Reposo mín. 1 h a 4 °C</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="25" t="n">
@@ -1393,26 +1519,31 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Retirar pesos y dorar 5 min más</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
+          <t>Estirar y forrar moldes de tarta</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Espesor 2,5-3 mm</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Ayudante</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="25" t="n">
@@ -1420,69 +1551,179 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
+          <t>Hornear en blanco con pesos (180 °C, 15 min)</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>180 °C · 15 min</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="n"/>
+      <c r="H33" s="15" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Retirar pesos y dorar 5 min más</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>180 °C · 5 min más</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
           <t>Enfriar bases antes de rellenar</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Hasta 20-22 °C</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Ayudante</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="15" t="n"/>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="15" t="n"/>
+    </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="15" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="15" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="13" t="n"/>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="15" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D36" s="16">
-        <f>COUNTIF(F5:F34,"✓")</f>
+      <c r="E41" s="16">
+        <f>COUNTIF(G5:G39,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F36" s="16" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="G41" s="16">
+        <f>COUNTIF(B5:B39,"?*")</f>
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="24" t="n"/>
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F38" s="15" t="n"/>
-      <c r="G38" s="24" t="n"/>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="24" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1490,18 +1731,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B43:E43"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H39">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$G5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F19 F20 F21 F22 F23 F24 F25 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G21 G22 G23 G24 G25 G26 G27 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1524,16 +1770,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1564,25 +1811,30 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>Parámetro / Objetivo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Hora Límite</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
       <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
@@ -1599,7 +1851,8 @@
       <c r="D5" s="23" t="n"/>
       <c r="E5" s="23" t="n"/>
       <c r="F5" s="23" t="n"/>
-      <c r="G5" s="24" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="25" t="n">
@@ -1610,23 +1863,28 @@
           <t>Preparar crema pastelera (leche, yemas, azúcar, maicena, vainilla)</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Hervir 1-2 min sin dejar de remover</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
@@ -1634,26 +1892,31 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Enfriar rápidamente en baño maría inverso (abatir a &lt;4 °C en 2h)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>Enfriar rápido en baño maría invertido o abatidor, tapar y etiquetar</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>De +65 °C a +10 °C en menos de 2 h · después ≤4 °C</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>06:30</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n">
@@ -1664,23 +1927,28 @@
           <t>Preparar crema de mantequilla (merengue suizo o italiana)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Almíbar a 118-121 °C · mantequilla a 18-20 °C</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>06:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="25" t="n">
@@ -1688,26 +1956,31 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Preparar ganache de chocolate (55% para relleno, 70% para cobertura)</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+          <t>Preparar ganache de relleno o de baño según el uso</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Relleno 2:1 chocolate:nata · baño 1:1 · nata a 80-85 °C</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="25" t="n">
@@ -1718,23 +1991,28 @@
           <t>Preparar crema diplomática (pastelera + nata montada)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>2 partes de pastelera por 1 de nata montada</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
@@ -1745,23 +2023,28 @@
           <t>Preparar lemon curd / curd de frutas de temporada</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Cocer hasta 82-84 °C</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n">
@@ -1769,26 +2052,31 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Etiquetar todas las cremas con fecha y hora de elaboración</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+          <t>Etiquetar todas las cremas con fecha y hora de elaboración → 13 Registro de Temperaturas · Etiquetas de Elaborado</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Vida útil orientativa 48-72 h a ≤4 °C</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Ayudante</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13"/>
     <row r="14">
@@ -1802,7 +2090,8 @@
       <c r="D14" s="23" t="n"/>
       <c r="E14" s="23" t="n"/>
       <c r="F14" s="23" t="n"/>
-      <c r="G14" s="24" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="24" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
@@ -1813,23 +2102,28 @@
           <t>Preparar mousse de chocolate (templar chocolate + merengue + nata)</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Chocolate a 45-50 °C · mezcla final a 28-30 °C</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n">
@@ -1840,23 +2134,28 @@
           <t>Preparar mousse de frutas (puré + gelatina + merengue + nata)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Gelatina 10-12 g por litro · puré a 25-30 °C</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="25" t="n">
@@ -1867,23 +2166,28 @@
           <t>Preparar compota / confit de frutas para rellenos</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Cocer hasta 60-62 °Brix</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Ayudante</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>07:30</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="25" t="n">
@@ -1894,23 +2198,28 @@
           <t>Preparar pralinés y praliné de frutos secos</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Tueste a 160 °C 12-15 min · caramelo a 170 °C</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="25" t="n">
@@ -1921,23 +2230,28 @@
           <t>Montar entremet en aros (capas de mousse + inserto + bizcocho)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Aro de 16-18 cm · inserto congelado</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="25" t="n">
@@ -1948,23 +2262,28 @@
           <t>Congelar entremets montados para el glaseado de mañana (mín. 4 h en abatidor a −18 °C o 12 h en congelador)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Mín. 4 h a −18 °C en abatidor · 12 h en congelador</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21"/>
     <row r="22">
@@ -1978,7 +2297,8 @@
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="23" t="n"/>
       <c r="F22" s="23" t="n"/>
-      <c r="G22" s="24" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="25" t="n">
@@ -1986,26 +2306,31 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Preparar glasé espejo (gelatina + glucosa + chocolate blanco + colorante)</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+          <t>Preparar el glaseado espejo para el día siguiente (gelatina, glucosa, chocolate blanco y colorante)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Reposo mínimo 12 h en frío antes de usarlo</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="25" t="n">
@@ -2013,26 +2338,31 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Temperar chocolate de cobertura (curva: 45°→27°→31° negro / 29° leche)</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+          <t>Temperar el chocolate de cobertura siguiendo su curva</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Negro 50-55 → 28-29 → 31-32 °C · leche 45 → 27-28 → 29-30 °C · blanco 40-45 → 26-27 → 28-29 °C</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="25" t="n">
@@ -2043,23 +2373,28 @@
           <t>Preparar fondant para glaseado de bollería</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Uso a 35-37 °C</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>Ayudante</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
+      <c r="G25" s="14" t="n"/>
+      <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="25" t="n">
@@ -2070,23 +2405,28 @@
           <t>Preparar merengue italiano para decoración (almíbar 121 °C + claras)</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Almíbar a 121 °C</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="25" t="n">
@@ -2097,66 +2437,112 @@
           <t>Preparar caramelo para decoraciones (160-170 °C)</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>160-170 °C</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
+      <c r="G27" s="14" t="n"/>
+      <c r="H27" s="15" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="14" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="15" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D30" s="16">
-        <f>COUNTIF(F5:F28,"✓")</f>
+      <c r="E33" s="16">
+        <f>COUNTIF(G5:G31,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="G33" s="16">
+        <f>COUNTIF(B5:B31,"?*")</f>
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="24" t="n"/>
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F32" s="15" t="n"/>
-      <c r="G32" s="24" t="n"/>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="24" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2164,18 +2550,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B35:E35"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H31">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$G5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G12 G15 G16 G17 G18 G19 G20 G23 G24 G25 G26 G27 G28 G29 G30 G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2198,16 +2589,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2238,25 +2630,30 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
+          <t>Parámetro / Objetivo</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Hora Límite</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Hecha</t>
-        </is>
-      </c>
       <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>✓ Completada</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Firma</t>
         </is>
@@ -2273,7 +2670,8 @@
       <c r="D5" s="23" t="n"/>
       <c r="E5" s="23" t="n"/>
       <c r="F5" s="23" t="n"/>
-      <c r="G5" s="24" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="24" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="25" t="n">
@@ -2284,23 +2682,28 @@
           <t>Desmoldar los entremets congelados el día anterior</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Pieza a −18 °C · sin condensación</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
@@ -2308,26 +2711,31 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Glasear con glasé espejo a 35 °C (sobre rejilla)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
+          <t>Glasear con glaseado espejo sobre rejilla</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Glaseado a 32-35 °C · pieza a −18 °C</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
+      <c r="G7" s="14" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n">
@@ -2338,23 +2746,24 @@
           <t>Decorar con frutas frescas, flores comestibles, láminas de chocolate</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="25" t="n">
@@ -2365,23 +2774,24 @@
           <t>Colocar etiquetas de chocolate / logotipos</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>10:45</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
+      <c r="G9" s="14" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="25" t="n">
@@ -2389,26 +2799,31 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Montar tartas por encargo (según la ficha de encargo de cada pedido)</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pastelero</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+          <t>Montar tartas por encargo (según la ficha de encargo de cada pedido) → 11 Control de Encargos · Ficha de Encargo</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Raciones, dedicatoria y hora de recogida</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Pastelero</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
@@ -2419,23 +2834,24 @@
           <t>Fotografiar piezas especiales para RRSS (si aplica)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Obrador</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12"/>
     <row r="13">
@@ -2449,7 +2865,8 @@
       <c r="D13" s="23" t="n"/>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="n"/>
-      <c r="G13" s="24" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="24" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="25" t="n">
@@ -2460,23 +2877,24 @@
           <t>Seleccionar piezas para vitrina (variedad, colores, tamaños)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Jefe Pastelero</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
@@ -2487,23 +2905,28 @@
           <t>Montar vitrina de bollería (croissants, pain au chocolat, napolitanas)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Ambiente · reponer en tandas pequeñas</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="G15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n">
@@ -2514,23 +2937,28 @@
           <t>Montar vitrina de pastelería (tartas individuales, entremets, macarons)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Vitrina refrigerada a 2-6 °C</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="25" t="n">
@@ -2541,23 +2969,28 @@
           <t>Montar vitrina de pan (si aplica)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Ambiente seco · nunca en frío</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="25" t="n">
@@ -2565,26 +2998,31 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Colocar etiquetas de alérgenos e ingredientes</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
+          <t>Colocar etiquetas de alérgenos e ingredientes → 12 Control de Alérgenos de Vitrina</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Los 14 alérgenos de declaración obligatoria</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="25" t="n">
@@ -2595,23 +3033,24 @@
           <t>Actualizar pizarra / carta del día</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="25" t="n">
@@ -2622,66 +3061,112 @@
           <t>Reponer vitrina cada 2 horas durante servicio</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Cada 2 h · retirar lo que lleve más de un día</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>Vitrina</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Dependiente</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Continuo</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="15" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="15" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D23" s="16">
-        <f>COUNTIF(F5:F21,"✓")</f>
+      <c r="E26" s="16">
+        <f>COUNTIF(G5:G24,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="G26" s="16">
+        <f>COUNTIF(B5:B24,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="24" t="n"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="24" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2689,17 +3174,22 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:H24">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$G5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="G6 G7 G8 G9 G10 G11 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/02-partidas-cocina.xlsx
@@ -682,7 +682,7 @@
     <row r="11">
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Vida útil orientativa 48-72 h a ≤4 °C</t>
+          <t>24 h de tope a ≤4 °C (art. 9.3)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Vitrina refrigerada a 2-6 °C</t>
+          <t>Vitrina refrigerada a 0-4 °C (art. 4.1, fila 9)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
